--- a/output/yearly_benthic_cover_iteration_94_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_94_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.29817174096445</v>
+        <v>45.08433700912327</v>
       </c>
       <c r="M2" t="n">
-        <v>99.8291431169084</v>
+        <v>100.4401493315559</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.0539285888438</v>
+        <v>88.07183566696926</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92973852035464</v>
+        <v>45.92224574006352</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228798082782503</v>
+        <v>2.228849666113632</v>
       </c>
       <c r="E3" t="n">
-        <v>5.708446565393918</v>
+        <v>5.705207915253029</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429326942608345</v>
+        <v>0.742949888704544</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97320313959113</v>
+        <v>33.97040173198243</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17490393599839</v>
+        <v>34.17569488040902</v>
       </c>
       <c r="I3" t="n">
-        <v>6.58231483168681</v>
+        <v>6.605294780103214</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643329339130215</v>
+        <v>4.643436804403399</v>
       </c>
       <c r="K3" t="n">
-        <v>11.9460714111562</v>
+        <v>11.92816433303074</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88792587273144</v>
+        <v>48.91250638087652</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7637358042423</v>
+        <v>106.7629164539708</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.02545718517969</v>
+        <v>87.25038547134457</v>
       </c>
       <c r="C4" t="n">
-        <v>42.53911947165415</v>
+        <v>42.74336105922106</v>
       </c>
       <c r="D4" t="n">
-        <v>2.178681411545178</v>
+        <v>2.189762572677246</v>
       </c>
       <c r="E4" t="n">
-        <v>6.496221857240012</v>
+        <v>6.524491646130516</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444968958680176</v>
+        <v>0.7445155438809703</v>
       </c>
       <c r="G4" t="n">
-        <v>33.20928295059844</v>
+        <v>33.37466650283852</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24685720992881</v>
+        <v>34.24771501852463</v>
       </c>
       <c r="I4" t="n">
-        <v>5.496811260824135</v>
+        <v>5.51601203803662</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65310559917511</v>
+        <v>4.653222149256064</v>
       </c>
       <c r="K4" t="n">
-        <v>12.97454281482028</v>
+        <v>12.74961452865543</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30349563486762</v>
+        <v>44.3235440015651</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81715792134204</v>
+        <v>99.81651958944158</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.86012012027841</v>
+        <v>86.22311102076667</v>
       </c>
       <c r="C5" t="n">
-        <v>42.22679205879813</v>
+        <v>42.57227459801001</v>
       </c>
       <c r="D5" t="n">
-        <v>2.121837670944076</v>
+        <v>2.140119602849197</v>
       </c>
       <c r="E5" t="n">
-        <v>7.091535736872494</v>
+        <v>7.144054910537863</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458232293664332</v>
+        <v>0.7458409385934128</v>
       </c>
       <c r="G5" t="n">
-        <v>32.34282314808256</v>
+        <v>32.61804677479377</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30786855085592</v>
+        <v>34.30868317529698</v>
       </c>
       <c r="I5" t="n">
-        <v>4.588836600616718</v>
+        <v>4.604859752486616</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661395183540207</v>
+        <v>4.661505866208829</v>
       </c>
       <c r="K5" t="n">
-        <v>14.1398798797216</v>
+        <v>13.77688897923332</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48063885979069</v>
+        <v>43.49761386614455</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84731079831042</v>
+        <v>99.84677744338788</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.44707390736893</v>
+        <v>85.04311575684986</v>
       </c>
       <c r="C6" t="n">
-        <v>41.52631198910841</v>
+        <v>42.10763081736943</v>
       </c>
       <c r="D6" t="n">
-        <v>2.05278682596455</v>
+        <v>2.082985372474611</v>
       </c>
       <c r="E6" t="n">
-        <v>7.499058179267813</v>
+        <v>7.593859155294278</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469507056853301</v>
+        <v>0.7469644427216869</v>
       </c>
       <c r="G6" t="n">
-        <v>31.29029245830328</v>
+        <v>31.74725105089168</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35973246152518</v>
+        <v>34.36036436519759</v>
       </c>
       <c r="I6" t="n">
-        <v>3.829811366089453</v>
+        <v>3.843163603259456</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668441910533312</v>
+        <v>4.668527767010542</v>
       </c>
       <c r="K6" t="n">
-        <v>15.55292609263108</v>
+        <v>14.95688424315016</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79329423491006</v>
+        <v>42.80757216857799</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87253231664955</v>
+        <v>99.87208722909757</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.79718942555651</v>
+        <v>83.74590237541896</v>
       </c>
       <c r="C7" t="n">
-        <v>40.47112193269876</v>
+        <v>41.40761936262631</v>
       </c>
       <c r="D7" t="n">
-        <v>1.972395440141451</v>
+        <v>2.020331193098254</v>
       </c>
       <c r="E7" t="n">
-        <v>7.737982092173546</v>
+        <v>7.899897252881972</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479116751787472</v>
+        <v>0.7479178461330633</v>
       </c>
       <c r="G7" t="n">
-        <v>30.06489976690625</v>
+        <v>30.79232453612422</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40393705822236</v>
+        <v>34.40422092212091</v>
       </c>
       <c r="I7" t="n">
-        <v>3.195615423066983</v>
+        <v>3.206724086728899</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674447969867169</v>
+        <v>4.674486538331645</v>
       </c>
       <c r="K7" t="n">
-        <v>17.20281057444349</v>
+        <v>16.25409762458104</v>
       </c>
       <c r="L7" t="n">
-        <v>42.2196838437997</v>
+        <v>42.23152846825768</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89361635094194</v>
+        <v>99.89324545546502</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.52945797128348</v>
+        <v>88.77314894104833</v>
       </c>
       <c r="C8" t="n">
-        <v>42.73106870584654</v>
+        <v>43.79057134837638</v>
       </c>
       <c r="D8" t="n">
-        <v>1.976562127233265</v>
+        <v>2.024674782354323</v>
       </c>
       <c r="E8" t="n">
-        <v>9.53753459980444</v>
+        <v>9.791716404853343</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494916392464804</v>
+        <v>0.7495258240388559</v>
       </c>
       <c r="G8" t="n">
-        <v>30.55774975956431</v>
+        <v>31.31880140364831</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47661540533809</v>
+        <v>34.47818790578737</v>
       </c>
       <c r="I8" t="n">
-        <v>5.547181694806399</v>
+        <v>5.725706220123293</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684322745290502</v>
+        <v>4.684536400242849</v>
       </c>
       <c r="K8" t="n">
-        <v>12.47054202871653</v>
+        <v>11.22685105895166</v>
       </c>
       <c r="L8" t="n">
-        <v>44.61387299971605</v>
+        <v>44.79213016905197</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81548373427911</v>
+        <v>99.80955257638001</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.31806339484633</v>
+        <v>87.09331722996815</v>
       </c>
       <c r="C9" t="n">
-        <v>41.3803854514678</v>
+        <v>43.00012367883177</v>
       </c>
       <c r="D9" t="n">
-        <v>1.876057649595858</v>
+        <v>1.949386948092363</v>
       </c>
       <c r="E9" t="n">
-        <v>9.824404724039763</v>
+        <v>10.22430183905434</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508477050337304</v>
+        <v>0.7508970914346422</v>
       </c>
       <c r="G9" t="n">
-        <v>29.0039454874676</v>
+        <v>30.15420709452214</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53899443155159</v>
+        <v>34.54126620599353</v>
       </c>
       <c r="I9" t="n">
-        <v>4.631015240696988</v>
+        <v>4.780151229404622</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692798156460815</v>
+        <v>4.693106821466513</v>
       </c>
       <c r="K9" t="n">
-        <v>14.68193660515367</v>
+        <v>12.90668277003185</v>
       </c>
       <c r="L9" t="n">
-        <v>43.78358956296725</v>
+        <v>43.93414615613295</v>
       </c>
       <c r="M9" t="n">
-        <v>99.8459116195887</v>
+        <v>99.84095260499657</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.97666742572827</v>
+        <v>85.30959719249279</v>
       </c>
       <c r="C10" t="n">
-        <v>39.75705615822677</v>
+        <v>41.95898282860097</v>
       </c>
       <c r="D10" t="n">
-        <v>1.770888619924124</v>
+        <v>1.870149580646728</v>
       </c>
       <c r="E10" t="n">
-        <v>9.917858321578139</v>
+        <v>10.4736561664533</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520135569504642</v>
+        <v>0.7520676635119291</v>
       </c>
       <c r="G10" t="n">
-        <v>27.37802700664376</v>
+        <v>28.92851919817165</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59262361972134</v>
+        <v>34.59511252154873</v>
       </c>
       <c r="I10" t="n">
-        <v>3.865171569970042</v>
+        <v>3.9896691652109</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700084730940401</v>
+        <v>4.700422896949556</v>
       </c>
       <c r="K10" t="n">
-        <v>17.02333257427175</v>
+        <v>14.69040280750722</v>
       </c>
       <c r="L10" t="n">
-        <v>43.0909719552599</v>
+        <v>43.21783238529723</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87136068775841</v>
+        <v>99.86721802140542</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.50302230178005</v>
+        <v>83.43410415823914</v>
       </c>
       <c r="C11" t="n">
-        <v>37.88197176586634</v>
+        <v>40.70302029192037</v>
       </c>
       <c r="D11" t="n">
-        <v>1.660974028747445</v>
+        <v>1.787540783574429</v>
       </c>
       <c r="E11" t="n">
-        <v>9.839828167888903</v>
+        <v>10.56586847292027</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530178474632353</v>
+        <v>0.7530679512422187</v>
       </c>
       <c r="G11" t="n">
-        <v>25.67874190660836</v>
+        <v>27.65068014359857</v>
       </c>
       <c r="H11" t="n">
-        <v>34.6388209833088</v>
+        <v>34.64112575714205</v>
       </c>
       <c r="I11" t="n">
-        <v>3.225277821118074</v>
+        <v>3.329146354497717</v>
       </c>
       <c r="J11" t="n">
-        <v>4.70636154664522</v>
+        <v>4.706674695263866</v>
       </c>
       <c r="K11" t="n">
-        <v>19.49697769821995</v>
+        <v>16.56589584176086</v>
       </c>
       <c r="L11" t="n">
-        <v>42.51368465897011</v>
+        <v>42.6202597228407</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8926341230564</v>
+        <v>99.88917585652194</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.00895808911379</v>
+        <v>81.41830327176228</v>
       </c>
       <c r="C12" t="n">
-        <v>35.88645299097476</v>
+        <v>39.20373790298331</v>
       </c>
       <c r="D12" t="n">
-        <v>1.551334856403882</v>
+        <v>1.699397038816143</v>
       </c>
       <c r="E12" t="n">
-        <v>9.638781627763894</v>
+        <v>10.50777207187227</v>
       </c>
       <c r="F12" t="n">
-        <v>0.753883661222109</v>
+        <v>0.7539242711966877</v>
       </c>
       <c r="G12" t="n">
-        <v>23.98371479556579</v>
+        <v>26.28722342397241</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67864841621699</v>
+        <v>34.68051647504763</v>
       </c>
       <c r="I12" t="n">
-        <v>2.690821849302928</v>
+        <v>2.77744329587785</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711772882638181</v>
+        <v>4.712026694979297</v>
       </c>
       <c r="K12" t="n">
-        <v>21.99104191088621</v>
+        <v>18.58169672823772</v>
       </c>
       <c r="L12" t="n">
-        <v>42.03291404755242</v>
+        <v>42.12208908115401</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91040894941339</v>
+        <v>99.90752371237504</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.48045144992487</v>
+        <v>79.26498664071521</v>
       </c>
       <c r="C13" t="n">
-        <v>33.77293355861436</v>
+        <v>37.48075618812681</v>
       </c>
       <c r="D13" t="n">
-        <v>1.441242773143906</v>
+        <v>1.60589847694303</v>
       </c>
       <c r="E13" t="n">
-        <v>9.328851224016196</v>
+        <v>10.31578029445889</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546309398522817</v>
+        <v>0.7546588052816023</v>
       </c>
       <c r="G13" t="n">
-        <v>22.2816856590081</v>
+        <v>24.84093539966773</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71302323320494</v>
+        <v>34.7143050429537</v>
       </c>
       <c r="I13" t="n">
-        <v>2.244574246622688</v>
+        <v>2.316791088400258</v>
       </c>
       <c r="J13" t="n">
-        <v>4.71644337407676</v>
+        <v>4.716617533010014</v>
       </c>
       <c r="K13" t="n">
-        <v>24.51954855007515</v>
+        <v>20.73501335928479</v>
       </c>
       <c r="L13" t="n">
-        <v>41.63277283994095</v>
+        <v>41.70707924992513</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92525494863045</v>
+        <v>99.92284879733671</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.68148944071118</v>
+        <v>85.13671282183093</v>
       </c>
       <c r="C14" t="n">
-        <v>38.27723991820118</v>
+        <v>41.04781026260125</v>
       </c>
       <c r="D14" t="n">
-        <v>1.442920184487621</v>
+        <v>1.607815288920344</v>
       </c>
       <c r="E14" t="n">
-        <v>11.81830025624631</v>
+        <v>12.34951844708729</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555092280369057</v>
+        <v>0.7555595714617303</v>
       </c>
       <c r="G14" t="n">
-        <v>24.30505977130226</v>
+        <v>26.38391191682065</v>
       </c>
       <c r="H14" t="n">
-        <v>36.75086573837022</v>
+        <v>36.26906648515664</v>
       </c>
       <c r="I14" t="n">
-        <v>2.886901587037203</v>
+        <v>3.048593790748455</v>
       </c>
       <c r="J14" t="n">
-        <v>4.72193267523066</v>
+        <v>4.722247321635813</v>
       </c>
       <c r="K14" t="n">
-        <v>17.31851055928882</v>
+        <v>14.8632871781691</v>
       </c>
       <c r="L14" t="n">
-        <v>44.3081313381543</v>
+        <v>43.98740391571595</v>
       </c>
       <c r="M14" t="n">
-        <v>99.9038818156443</v>
+        <v>99.89850135648629</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.74005229720075</v>
+        <v>84.63526554693277</v>
       </c>
       <c r="C15" t="n">
-        <v>37.78085597388152</v>
+        <v>41.01877375366249</v>
       </c>
       <c r="D15" t="n">
-        <v>1.408088600633405</v>
+        <v>1.589420241729007</v>
       </c>
       <c r="E15" t="n">
-        <v>11.93481828699019</v>
+        <v>12.63206724113486</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562511540829383</v>
+        <v>0.7563163157787924</v>
       </c>
       <c r="G15" t="n">
-        <v>23.71879953206049</v>
+        <v>26.08205304774129</v>
       </c>
       <c r="H15" t="n">
-        <v>36.78741118918781</v>
+        <v>36.30539242289136</v>
       </c>
       <c r="I15" t="n">
-        <v>2.408113821227545</v>
+        <v>2.543039304040017</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726569713018363</v>
+        <v>4.726976973617452</v>
       </c>
       <c r="K15" t="n">
-        <v>18.25994770279925</v>
+        <v>15.36473445306724</v>
       </c>
       <c r="L15" t="n">
-        <v>43.87900461256819</v>
+        <v>43.53180863241616</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91980828924896</v>
+        <v>99.91531683914589</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.00975302682814</v>
+        <v>82.51286445502976</v>
       </c>
       <c r="C16" t="n">
-        <v>35.42211855634266</v>
+        <v>39.29065565781983</v>
       </c>
       <c r="D16" t="n">
-        <v>1.305461348678903</v>
+        <v>1.507010880399684</v>
       </c>
       <c r="E16" t="n">
-        <v>11.39970361069995</v>
+        <v>12.33061361134372</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568919617485312</v>
+        <v>0.7569643595484259</v>
       </c>
       <c r="G16" t="n">
-        <v>21.99007648541405</v>
+        <v>24.72973270011334</v>
       </c>
       <c r="H16" t="n">
-        <v>36.81858291694</v>
+        <v>36.33650041682579</v>
       </c>
       <c r="I16" t="n">
-        <v>2.008461942418376</v>
+        <v>2.121015239621147</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730574760928319</v>
+        <v>4.731027247177662</v>
       </c>
       <c r="K16" t="n">
-        <v>20.99024697317189</v>
+        <v>17.48713554497025</v>
       </c>
       <c r="L16" t="n">
-        <v>43.5207424198958</v>
+        <v>43.15156881654216</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93310794941033</v>
+        <v>99.92936001933222</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.69326380754759</v>
+        <v>84.06135547398416</v>
       </c>
       <c r="C17" t="n">
-        <v>36.64666654474168</v>
+        <v>40.42446317219514</v>
       </c>
       <c r="D17" t="n">
-        <v>1.306540876915533</v>
+        <v>1.508282159370675</v>
       </c>
       <c r="E17" t="n">
-        <v>12.17371054079338</v>
+        <v>13.06883072555286</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575178602062776</v>
+        <v>0.7576029168970152</v>
       </c>
       <c r="G17" t="n">
-        <v>22.43920158135364</v>
+        <v>25.12384849772064</v>
       </c>
       <c r="H17" t="n">
-        <v>37.27997018472871</v>
+        <v>36.74040741097409</v>
       </c>
       <c r="I17" t="n">
-        <v>2.001836137260809</v>
+        <v>2.12736553286254</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734486626289234</v>
+        <v>4.735018230606344</v>
       </c>
       <c r="K17" t="n">
-        <v>19.30673619245241</v>
+        <v>15.93864452601584</v>
       </c>
       <c r="L17" t="n">
-        <v>43.97992452540812</v>
+        <v>43.56603988679287</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93332726260221</v>
+        <v>99.92914758500385</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.03282570380915</v>
+        <v>81.95884459056917</v>
       </c>
       <c r="C18" t="n">
-        <v>34.29456555237218</v>
+        <v>38.65152085124602</v>
       </c>
       <c r="D18" t="n">
-        <v>1.210632307850468</v>
+        <v>1.429436156641221</v>
       </c>
       <c r="E18" t="n">
-        <v>11.55831234549914</v>
+        <v>12.68133343413837</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580580559497053</v>
+        <v>0.7581495534561709</v>
       </c>
       <c r="G18" t="n">
-        <v>20.79201873950421</v>
+        <v>23.8104901085634</v>
       </c>
       <c r="H18" t="n">
-        <v>37.3065550116573</v>
+        <v>36.76691687845526</v>
       </c>
       <c r="I18" t="n">
-        <v>1.669386393662683</v>
+        <v>1.774083750213689</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737862849685658</v>
+        <v>4.738434709101067</v>
       </c>
       <c r="K18" t="n">
-        <v>21.96717429619084</v>
+        <v>18.04115540943081</v>
       </c>
       <c r="L18" t="n">
-        <v>43.68265359206862</v>
+        <v>43.24823025229922</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94439344063164</v>
+        <v>99.94090651297606</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>76.88453431901392</v>
+        <v>81.03636499522776</v>
       </c>
       <c r="C19" t="n">
-        <v>33.38859801702633</v>
+        <v>38.00333017832074</v>
       </c>
       <c r="D19" t="n">
-        <v>1.169336442409048</v>
+        <v>1.395512071076956</v>
       </c>
       <c r="E19" t="n">
-        <v>11.39830542169921</v>
+        <v>12.62692421353742</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585199995040905</v>
+        <v>0.7586108824325504</v>
       </c>
       <c r="G19" t="n">
-        <v>20.08278241518491</v>
+        <v>23.24540778570684</v>
       </c>
       <c r="H19" t="n">
-        <v>37.329288788429</v>
+        <v>36.78928930359334</v>
       </c>
       <c r="I19" t="n">
-        <v>1.405551254887083</v>
+        <v>1.479302723677216</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740749996900565</v>
+        <v>4.741318015203438</v>
       </c>
       <c r="K19" t="n">
-        <v>23.11546568098609</v>
+        <v>18.96363500477224</v>
       </c>
       <c r="L19" t="n">
-        <v>43.44911312648293</v>
+        <v>42.9837547127344</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95317682449534</v>
+        <v>99.95071989582738</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.17333004148887</v>
+        <v>78.66129149668275</v>
       </c>
       <c r="C20" t="n">
-        <v>30.89295545333988</v>
+        <v>35.8568401658306</v>
       </c>
       <c r="D20" t="n">
-        <v>1.072802556355937</v>
+        <v>1.307259216086812</v>
       </c>
       <c r="E20" t="n">
-        <v>10.65264324752092</v>
+        <v>12.03395754629552</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589194768058773</v>
+        <v>0.7590073790454154</v>
       </c>
       <c r="G20" t="n">
-        <v>18.42486005940605</v>
+        <v>21.77535701006892</v>
       </c>
       <c r="H20" t="n">
-        <v>37.34894839341315</v>
+        <v>36.8085176444152</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1719095779502</v>
+        <v>1.233396581737035</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743246730036732</v>
+        <v>4.743796119033845</v>
       </c>
       <c r="K20" t="n">
-        <v>25.82666995851112</v>
+        <v>21.33870850331725</v>
       </c>
       <c r="L20" t="n">
-        <v>43.24133149773547</v>
+        <v>42.76335958852779</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96095690958647</v>
+        <v>99.95890825767565</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.62454146825029</v>
+        <v>83.72571556885629</v>
       </c>
       <c r="C21" t="n">
-        <v>34.96282142662681</v>
+        <v>38.90480670464889</v>
       </c>
       <c r="D21" t="n">
-        <v>1.073523312590018</v>
+        <v>1.308220834001772</v>
       </c>
       <c r="E21" t="n">
-        <v>12.82337773804015</v>
+        <v>13.71250790724058</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594293524962663</v>
+        <v>0.7595657037328957</v>
       </c>
       <c r="G21" t="n">
-        <v>20.32998059420935</v>
+        <v>23.15313057702409</v>
       </c>
       <c r="H21" t="n">
-        <v>39.26678296824199</v>
+        <v>38.19734958174296</v>
       </c>
       <c r="I21" t="n">
-        <v>1.62501404957086</v>
+        <v>1.847655316783369</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746433453101663</v>
+        <v>4.747285648330597</v>
       </c>
       <c r="K21" t="n">
-        <v>19.37545853174969</v>
+        <v>16.27428443114374</v>
       </c>
       <c r="L21" t="n">
-        <v>45.60758927408298</v>
+        <v>44.75936562476237</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94586923245947</v>
+        <v>99.938456760555</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_94_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_94_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.08433700912327</v>
+        <v>45.0639305211043</v>
       </c>
       <c r="M2" t="n">
-        <v>100.4401493315559</v>
+        <v>100.7718515870655</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.07183566696926</v>
+        <v>88.00976957710678</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92224574006352</v>
+        <v>45.88344488913012</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228849666113632</v>
+        <v>2.228719931819319</v>
       </c>
       <c r="E3" t="n">
-        <v>5.705207915253029</v>
+        <v>5.679693105717472</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742949888704544</v>
+        <v>0.7429066439397731</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97040173198243</v>
+        <v>33.95757538724743</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17569488040902</v>
+        <v>34.17370562122956</v>
       </c>
       <c r="I3" t="n">
-        <v>6.605294780103214</v>
+        <v>6.584002362529649</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643436804403399</v>
+        <v>4.643166524623582</v>
       </c>
       <c r="K3" t="n">
-        <v>11.92816433303074</v>
+        <v>11.99023042289322</v>
       </c>
       <c r="L3" t="n">
-        <v>48.91250638087652</v>
+        <v>48.8899916335258</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7629164539708</v>
+        <v>106.7636669455491</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.25038547134457</v>
+        <v>87.07844120529805</v>
       </c>
       <c r="C4" t="n">
-        <v>42.74336105922106</v>
+        <v>42.59201146948884</v>
       </c>
       <c r="D4" t="n">
-        <v>2.189762572677246</v>
+        <v>2.183727456268001</v>
       </c>
       <c r="E4" t="n">
-        <v>6.524491646130516</v>
+        <v>6.481403215318692</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445155438809703</v>
+        <v>0.7444702385760101</v>
       </c>
       <c r="G4" t="n">
-        <v>33.37466650283852</v>
+        <v>33.27205390983794</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24771501852463</v>
+        <v>34.24563097449646</v>
       </c>
       <c r="I4" t="n">
-        <v>5.51601203803662</v>
+        <v>5.498216419700901</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653222149256064</v>
+        <v>4.652938991100063</v>
       </c>
       <c r="K4" t="n">
-        <v>12.74961452865543</v>
+        <v>12.92155879470194</v>
       </c>
       <c r="L4" t="n">
-        <v>44.3235440015651</v>
+        <v>44.30354078129452</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81651958944158</v>
+        <v>99.81711104548529</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.22311102076667</v>
+        <v>86.00863949947096</v>
       </c>
       <c r="C5" t="n">
-        <v>42.57227459801001</v>
+        <v>42.37549428357646</v>
       </c>
       <c r="D5" t="n">
-        <v>2.140119602849197</v>
+        <v>2.131806911654411</v>
       </c>
       <c r="E5" t="n">
-        <v>7.144054910537863</v>
+        <v>7.092300261468274</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458409385934128</v>
+        <v>0.7457945693418048</v>
       </c>
       <c r="G5" t="n">
-        <v>32.61804677479377</v>
+        <v>32.48097389000623</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30868317529698</v>
+        <v>34.30655018972301</v>
       </c>
       <c r="I5" t="n">
-        <v>4.604859752486616</v>
+        <v>4.589997618890946</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661505866208829</v>
+        <v>4.661216058386279</v>
       </c>
       <c r="K5" t="n">
-        <v>13.77688897923332</v>
+        <v>13.99136050052902</v>
       </c>
       <c r="L5" t="n">
-        <v>43.49761386614455</v>
+        <v>43.48041698201394</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84677744338788</v>
+        <v>99.84727176611943</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.04311575684986</v>
+        <v>84.81549280614168</v>
       </c>
       <c r="C6" t="n">
-        <v>42.10763081736943</v>
+        <v>41.89522860843182</v>
       </c>
       <c r="D6" t="n">
-        <v>2.082985372474611</v>
+        <v>2.07393540846742</v>
       </c>
       <c r="E6" t="n">
-        <v>7.593859155294278</v>
+        <v>7.538227220146767</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469644427216869</v>
+        <v>0.7469173820929136</v>
       </c>
       <c r="G6" t="n">
-        <v>31.74725105089168</v>
+        <v>31.59922293324004</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36036436519759</v>
+        <v>34.35819957627402</v>
       </c>
       <c r="I6" t="n">
-        <v>3.843163603259456</v>
+        <v>3.830756647839805</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668527767010542</v>
+        <v>4.66823363808071</v>
       </c>
       <c r="K6" t="n">
-        <v>14.95688424315016</v>
+        <v>15.18450719385833</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80757216857799</v>
+        <v>42.79276426385174</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87208722909757</v>
+        <v>99.8725000661419</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.74590237541896</v>
+        <v>83.42787437104488</v>
       </c>
       <c r="C7" t="n">
-        <v>41.40761936262631</v>
+        <v>41.10273404327255</v>
       </c>
       <c r="D7" t="n">
-        <v>2.020331193098254</v>
+        <v>2.006663882354901</v>
       </c>
       <c r="E7" t="n">
-        <v>7.899897252881972</v>
+        <v>7.826441364240216</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479178461330633</v>
+        <v>0.7478712708608319</v>
       </c>
       <c r="G7" t="n">
-        <v>30.79232453612422</v>
+        <v>30.57424985933915</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40422092212091</v>
+        <v>34.40207845959826</v>
       </c>
       <c r="I7" t="n">
-        <v>3.206724086728899</v>
+        <v>3.196374091771317</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674486538331645</v>
+        <v>4.674195442880199</v>
       </c>
       <c r="K7" t="n">
-        <v>16.25409762458104</v>
+        <v>16.57212562895512</v>
       </c>
       <c r="L7" t="n">
-        <v>42.23152846825768</v>
+        <v>42.21873042088789</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89324545546502</v>
+        <v>99.89359009311556</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.77314894104833</v>
+        <v>88.40274441231358</v>
       </c>
       <c r="C8" t="n">
-        <v>43.79057134837638</v>
+        <v>43.43702215043626</v>
       </c>
       <c r="D8" t="n">
-        <v>2.024674782354323</v>
+        <v>2.010985597487832</v>
       </c>
       <c r="E8" t="n">
-        <v>9.791716404853343</v>
+        <v>9.685089327929141</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495258240388559</v>
+        <v>0.7494819474754779</v>
       </c>
       <c r="G8" t="n">
-        <v>31.31880140364831</v>
+        <v>31.08501479403617</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47818790578737</v>
+        <v>34.47616958387197</v>
       </c>
       <c r="I8" t="n">
-        <v>5.725706220123293</v>
+        <v>5.711740989791259</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684536400242849</v>
+        <v>4.684262171721737</v>
       </c>
       <c r="K8" t="n">
-        <v>11.22685105895166</v>
+        <v>11.5972555876864</v>
       </c>
       <c r="L8" t="n">
-        <v>44.79213016905197</v>
+        <v>44.77574005673544</v>
       </c>
       <c r="M8" t="n">
-        <v>99.80955257638001</v>
+        <v>99.8100177948581</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>87.09331722996815</v>
+        <v>86.65470759477857</v>
       </c>
       <c r="C9" t="n">
-        <v>43.00012367883177</v>
+        <v>42.57583220908683</v>
       </c>
       <c r="D9" t="n">
-        <v>1.949386948092363</v>
+        <v>1.932354679142095</v>
       </c>
       <c r="E9" t="n">
-        <v>10.22430183905434</v>
+        <v>10.10114818479347</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508970914346422</v>
+        <v>0.7508567202263109</v>
       </c>
       <c r="G9" t="n">
-        <v>30.15420709452214</v>
+        <v>29.86956936116022</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54126620599353</v>
+        <v>34.53940913041028</v>
       </c>
       <c r="I9" t="n">
-        <v>4.780151229404622</v>
+        <v>4.768515017631748</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693106821466513</v>
+        <v>4.692854501414443</v>
       </c>
       <c r="K9" t="n">
-        <v>12.90668277003185</v>
+        <v>13.34529240522143</v>
       </c>
       <c r="L9" t="n">
-        <v>43.93414615613295</v>
+        <v>43.92021591375309</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84095260499657</v>
+        <v>99.84134052806134</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>85.30959719249279</v>
+        <v>84.71658635139288</v>
       </c>
       <c r="C10" t="n">
-        <v>41.95898282860097</v>
+        <v>41.37810145438527</v>
       </c>
       <c r="D10" t="n">
-        <v>1.870149580646728</v>
+        <v>1.845864576663766</v>
       </c>
       <c r="E10" t="n">
-        <v>10.4736561664533</v>
+        <v>10.31236263725277</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520676635119291</v>
+        <v>0.7520325619093663</v>
       </c>
       <c r="G10" t="n">
-        <v>28.92851919817165</v>
+        <v>28.53263978869827</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59511252154873</v>
+        <v>34.59349784783083</v>
       </c>
       <c r="I10" t="n">
-        <v>3.9896691652109</v>
+        <v>3.979985427104337</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700422896949556</v>
+        <v>4.700203511933539</v>
       </c>
       <c r="K10" t="n">
-        <v>14.69040280750722</v>
+        <v>15.28341364860711</v>
       </c>
       <c r="L10" t="n">
-        <v>43.21783238529723</v>
+        <v>43.20602614651785</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86721802140542</v>
+        <v>99.86754124951023</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>83.43410415823914</v>
+        <v>82.54403799372859</v>
       </c>
       <c r="C11" t="n">
-        <v>40.70302029192037</v>
+        <v>39.82312696062438</v>
       </c>
       <c r="D11" t="n">
-        <v>1.787540783574429</v>
+        <v>1.749654405723491</v>
       </c>
       <c r="E11" t="n">
-        <v>10.56586847292027</v>
+        <v>10.32837867975816</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530679512422187</v>
+        <v>0.7530411456836482</v>
       </c>
       <c r="G11" t="n">
-        <v>27.65068014359857</v>
+        <v>27.04546126750387</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64112575714205</v>
+        <v>34.63989270144781</v>
       </c>
       <c r="I11" t="n">
-        <v>3.329146354497717</v>
+        <v>3.321102633088821</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706674695263866</v>
+        <v>4.706507160522801</v>
       </c>
       <c r="K11" t="n">
-        <v>16.56589584176086</v>
+        <v>17.4559620062714</v>
       </c>
       <c r="L11" t="n">
-        <v>42.6202597228407</v>
+        <v>42.61035588235131</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88917585652194</v>
+        <v>99.8894448492471</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>81.41830327176228</v>
+        <v>80.17108223273243</v>
       </c>
       <c r="C12" t="n">
-        <v>39.20373790298331</v>
+        <v>37.96484399226868</v>
       </c>
       <c r="D12" t="n">
-        <v>1.699397038816143</v>
+        <v>1.645426077525483</v>
       </c>
       <c r="E12" t="n">
-        <v>10.50777207187227</v>
+        <v>10.17490445021787</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539242711966877</v>
+        <v>0.7539086682621501</v>
       </c>
       <c r="G12" t="n">
-        <v>26.28722342397241</v>
+        <v>25.43434126344212</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68051647504763</v>
+        <v>34.67979874005889</v>
       </c>
       <c r="I12" t="n">
-        <v>2.77744329587785</v>
+        <v>2.770773856587469</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712026694979297</v>
+        <v>4.711929176638438</v>
       </c>
       <c r="K12" t="n">
-        <v>18.58169672823772</v>
+        <v>19.82891776726756</v>
       </c>
       <c r="L12" t="n">
-        <v>42.12208908115401</v>
+        <v>42.11398538954463</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90752371237504</v>
+        <v>99.90774714908088</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>79.26498664071521</v>
+        <v>77.93400771317367</v>
       </c>
       <c r="C13" t="n">
-        <v>37.48075618812681</v>
+        <v>36.15633564219268</v>
       </c>
       <c r="D13" t="n">
-        <v>1.60589847694303</v>
+        <v>1.548150187599273</v>
       </c>
       <c r="E13" t="n">
-        <v>10.31578029445889</v>
+        <v>9.958584737612991</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546588052816023</v>
+        <v>0.7546539481797164</v>
       </c>
       <c r="G13" t="n">
-        <v>24.84093539966773</v>
+        <v>23.9306892824251</v>
       </c>
       <c r="H13" t="n">
-        <v>34.7143050429537</v>
+        <v>34.71408161626695</v>
       </c>
       <c r="I13" t="n">
-        <v>2.316791088400258</v>
+        <v>2.311260764966423</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716617533010014</v>
+        <v>4.716587176123228</v>
       </c>
       <c r="K13" t="n">
-        <v>20.73501335928479</v>
+        <v>22.06599228682633</v>
       </c>
       <c r="L13" t="n">
-        <v>41.70707924992513</v>
+        <v>41.70070613052022</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92284879733671</v>
+        <v>99.92303405953923</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>85.13671282183093</v>
+        <v>84.23900272106761</v>
       </c>
       <c r="C14" t="n">
-        <v>41.04781026260125</v>
+        <v>39.93087228734333</v>
       </c>
       <c r="D14" t="n">
-        <v>1.607815288920344</v>
+        <v>1.550092354966942</v>
       </c>
       <c r="E14" t="n">
-        <v>12.34951844708729</v>
+        <v>12.10701644043436</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555595714617303</v>
+        <v>0.7556006678738243</v>
       </c>
       <c r="G14" t="n">
-        <v>26.38391191682065</v>
+        <v>25.56825643755624</v>
       </c>
       <c r="H14" t="n">
-        <v>36.26906648515664</v>
+        <v>36.36517662733306</v>
       </c>
       <c r="I14" t="n">
-        <v>3.048593790748455</v>
+        <v>3.170356018691796</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722247321635813</v>
+        <v>4.722504174211402</v>
       </c>
       <c r="K14" t="n">
-        <v>14.8632871781691</v>
+        <v>15.76099727893238</v>
       </c>
       <c r="L14" t="n">
-        <v>43.98740391571595</v>
+        <v>44.20258430826566</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89850135648629</v>
+        <v>99.89445387454137</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>84.63526554693277</v>
+        <v>83.55587321602154</v>
       </c>
       <c r="C15" t="n">
-        <v>41.01877375366249</v>
+        <v>39.73816362060361</v>
       </c>
       <c r="D15" t="n">
-        <v>1.589420241729007</v>
+        <v>1.524703708447043</v>
       </c>
       <c r="E15" t="n">
-        <v>12.63206724113486</v>
+        <v>12.34950989402651</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563163157787924</v>
+        <v>0.7563978891116656</v>
       </c>
       <c r="G15" t="n">
-        <v>26.08205304774129</v>
+        <v>25.14947918035399</v>
       </c>
       <c r="H15" t="n">
-        <v>36.30539242289136</v>
+        <v>36.40354489824359</v>
       </c>
       <c r="I15" t="n">
-        <v>2.543039304040017</v>
+        <v>2.644750838890848</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726976973617452</v>
+        <v>4.72748680694791</v>
       </c>
       <c r="K15" t="n">
-        <v>15.36473445306724</v>
+        <v>16.44412678397844</v>
       </c>
       <c r="L15" t="n">
-        <v>43.53180863241616</v>
+        <v>43.72964415045429</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91531683914589</v>
+        <v>99.91193455503634</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>82.51286445502976</v>
+        <v>81.25752330056343</v>
       </c>
       <c r="C16" t="n">
-        <v>39.29065565781983</v>
+        <v>37.8490672618826</v>
       </c>
       <c r="D16" t="n">
-        <v>1.507010880399684</v>
+        <v>1.436202825968505</v>
       </c>
       <c r="E16" t="n">
-        <v>12.33061361134372</v>
+        <v>12.00034590818426</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569643595484259</v>
+        <v>0.7570823707701267</v>
       </c>
       <c r="G16" t="n">
-        <v>24.72973270011334</v>
+        <v>23.68968663901888</v>
       </c>
       <c r="H16" t="n">
-        <v>36.33650041682579</v>
+        <v>36.43648729422922</v>
       </c>
       <c r="I16" t="n">
-        <v>2.121015239621147</v>
+        <v>2.205953445079144</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731027247177662</v>
+        <v>4.731764817313293</v>
       </c>
       <c r="K16" t="n">
-        <v>17.48713554497025</v>
+        <v>18.74247669943656</v>
       </c>
       <c r="L16" t="n">
-        <v>43.15156881654216</v>
+        <v>43.33499073760053</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92936001933222</v>
+        <v>99.92653469891968</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>84.06135547398416</v>
+        <v>82.73579972371012</v>
       </c>
       <c r="C17" t="n">
-        <v>40.42446317219514</v>
+        <v>38.93428053321664</v>
       </c>
       <c r="D17" t="n">
-        <v>1.508282159370675</v>
+        <v>1.437487793893446</v>
       </c>
       <c r="E17" t="n">
-        <v>13.06883072555286</v>
+        <v>12.722093041507</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576029168970152</v>
+        <v>0.7577597309210662</v>
       </c>
       <c r="G17" t="n">
-        <v>25.12384849772064</v>
+        <v>24.05177439331544</v>
       </c>
       <c r="H17" t="n">
-        <v>36.74040741097409</v>
+        <v>36.80997958672289</v>
       </c>
       <c r="I17" t="n">
-        <v>2.12736553286254</v>
+        <v>2.22070685909363</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735018230606344</v>
+        <v>4.735998318256664</v>
       </c>
       <c r="K17" t="n">
-        <v>15.93864452601584</v>
+        <v>17.26420027628988</v>
       </c>
       <c r="L17" t="n">
-        <v>43.56603988679287</v>
+        <v>43.72756179806142</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92914758500385</v>
+        <v>99.92604260756794</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>81.95884459056917</v>
+        <v>80.56972067644519</v>
       </c>
       <c r="C18" t="n">
-        <v>38.65152085124602</v>
+        <v>37.11146742057944</v>
       </c>
       <c r="D18" t="n">
-        <v>1.429436156641221</v>
+        <v>1.357040211780844</v>
       </c>
       <c r="E18" t="n">
-        <v>12.68133343413837</v>
+        <v>12.31878152430978</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581495534561709</v>
+        <v>0.7583403362692945</v>
       </c>
       <c r="G18" t="n">
-        <v>23.8104901085634</v>
+        <v>22.70574063659094</v>
       </c>
       <c r="H18" t="n">
-        <v>36.76691687845526</v>
+        <v>36.83818387120004</v>
       </c>
       <c r="I18" t="n">
-        <v>1.774083750213689</v>
+        <v>1.852006994611171</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738434709101067</v>
+        <v>4.739627101683092</v>
       </c>
       <c r="K18" t="n">
-        <v>18.04115540943081</v>
+        <v>19.43027932355484</v>
       </c>
       <c r="L18" t="n">
-        <v>43.24823025229922</v>
+        <v>43.39656695422424</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94090651297606</v>
+        <v>99.93831369835851</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>81.03636499522776</v>
+        <v>79.72087215892222</v>
       </c>
       <c r="C19" t="n">
-        <v>38.00333017832074</v>
+        <v>36.54827738512394</v>
       </c>
       <c r="D19" t="n">
-        <v>1.395512071076956</v>
+        <v>1.326233808251339</v>
       </c>
       <c r="E19" t="n">
-        <v>12.62692421353742</v>
+        <v>12.29652003309442</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586108824325504</v>
+        <v>0.7588300165124574</v>
       </c>
       <c r="G19" t="n">
-        <v>23.24540778570684</v>
+        <v>22.19029370847878</v>
       </c>
       <c r="H19" t="n">
-        <v>36.78928930359334</v>
+        <v>36.86197125263418</v>
       </c>
       <c r="I19" t="n">
-        <v>1.479302723677216</v>
+        <v>1.544335736748199</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741318015203438</v>
+        <v>4.742687603202859</v>
       </c>
       <c r="K19" t="n">
-        <v>18.96363500477224</v>
+        <v>20.27912784107775</v>
       </c>
       <c r="L19" t="n">
-        <v>42.9837547127344</v>
+        <v>43.12115013505911</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95071989582738</v>
+        <v>99.9485553612608</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>78.66129149668275</v>
+        <v>77.38843596317268</v>
       </c>
       <c r="C20" t="n">
-        <v>35.8568401658306</v>
+        <v>34.45393244513579</v>
       </c>
       <c r="D20" t="n">
-        <v>1.307259216086812</v>
+        <v>1.240546367149019</v>
       </c>
       <c r="E20" t="n">
-        <v>12.03395754629552</v>
+        <v>11.7166567816339</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590073790454154</v>
+        <v>0.7592508869863845</v>
       </c>
       <c r="G20" t="n">
-        <v>21.77535701006892</v>
+        <v>20.75658762033772</v>
       </c>
       <c r="H20" t="n">
-        <v>36.8085176444152</v>
+        <v>36.88241603601569</v>
       </c>
       <c r="I20" t="n">
-        <v>1.233396581737035</v>
+        <v>1.287660227385054</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743796119033845</v>
+        <v>4.745318043664904</v>
       </c>
       <c r="K20" t="n">
-        <v>21.33870850331725</v>
+        <v>22.61156403682732</v>
       </c>
       <c r="L20" t="n">
-        <v>42.76335958852779</v>
+        <v>42.8916053031272</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95890825767565</v>
+        <v>99.95710178509032</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>83.72571556885629</v>
+        <v>82.74614734451288</v>
       </c>
       <c r="C21" t="n">
-        <v>38.90480670464889</v>
+        <v>37.65385103132368</v>
       </c>
       <c r="D21" t="n">
-        <v>1.308220834001772</v>
+        <v>1.241533036718635</v>
       </c>
       <c r="E21" t="n">
-        <v>13.71250790724058</v>
+        <v>13.48217579171718</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595657037328957</v>
+        <v>0.7598547578014793</v>
       </c>
       <c r="G21" t="n">
-        <v>23.15313057702409</v>
+        <v>22.20023546635771</v>
       </c>
       <c r="H21" t="n">
-        <v>38.19734958174296</v>
+        <v>38.33888957287959</v>
       </c>
       <c r="I21" t="n">
-        <v>1.847655316783369</v>
+        <v>1.974366482779052</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747285648330597</v>
+        <v>4.749092236259246</v>
       </c>
       <c r="K21" t="n">
-        <v>16.27428443114374</v>
+        <v>17.25385265548712</v>
       </c>
       <c r="L21" t="n">
-        <v>44.75936562476237</v>
+        <v>45.02653639929796</v>
       </c>
       <c r="M21" t="n">
-        <v>99.938456760555</v>
+        <v>99.93424008610876</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_94_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_94_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.0639305211043</v>
+        <v>43.78515868157474</v>
       </c>
       <c r="M2" t="n">
-        <v>100.7718515870655</v>
+        <v>94.85506786854279</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.00976957710678</v>
+        <v>81.41373468148869</v>
       </c>
       <c r="C3" t="n">
-        <v>45.88344488913012</v>
+        <v>43.16929023704425</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228719931819319</v>
+        <v>2.177034649312743</v>
       </c>
       <c r="E3" t="n">
-        <v>5.679693105717472</v>
+        <v>4.140605224554567</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429066439397731</v>
+        <v>0.7375883650079916</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95757538724743</v>
+        <v>32.74622951674586</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17370562122956</v>
+        <v>33.92906479036761</v>
       </c>
       <c r="I3" t="n">
-        <v>6.584002362529649</v>
+        <v>3.073284854199965</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643166524623582</v>
+        <v>4.609927281299948</v>
       </c>
       <c r="K3" t="n">
-        <v>11.99023042289322</v>
+        <v>18.58626531851131</v>
       </c>
       <c r="L3" t="n">
-        <v>48.8899916335258</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7636669455491</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.07844120529805</v>
+        <v>88.44229658611296</v>
       </c>
       <c r="C4" t="n">
-        <v>42.59201146948884</v>
+        <v>42.8085878188566</v>
       </c>
       <c r="D4" t="n">
-        <v>2.183727456268001</v>
+        <v>2.182682770064075</v>
       </c>
       <c r="E4" t="n">
-        <v>6.481403215318692</v>
+        <v>6.543728164556016</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444702385760101</v>
+        <v>0.7395019717352239</v>
       </c>
       <c r="G4" t="n">
-        <v>33.27205390983794</v>
+        <v>33.45373794646413</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24563097449646</v>
+        <v>34.0170906998203</v>
       </c>
       <c r="I4" t="n">
-        <v>5.498216419700901</v>
+        <v>6.883667710128059</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652938991100063</v>
+        <v>4.62188732334515</v>
       </c>
       <c r="K4" t="n">
-        <v>12.92155879470194</v>
+        <v>11.55770341388705</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30354078129452</v>
+        <v>45.40484693836638</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81711104548529</v>
+        <v>99.77113817111004</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.00863949947096</v>
+        <v>87.12111767070505</v>
       </c>
       <c r="C5" t="n">
-        <v>42.37549428357646</v>
+        <v>42.55453689715154</v>
       </c>
       <c r="D5" t="n">
-        <v>2.131806911654411</v>
+        <v>2.118966842055289</v>
       </c>
       <c r="E5" t="n">
-        <v>7.092300261468274</v>
+        <v>7.310874434277379</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457945693418048</v>
+        <v>0.7411285970615658</v>
       </c>
       <c r="G5" t="n">
-        <v>32.48097389000623</v>
+        <v>32.47717094925493</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30655018972301</v>
+        <v>34.09191546483203</v>
       </c>
       <c r="I5" t="n">
-        <v>4.589997618890946</v>
+        <v>5.74900765158907</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661216058386279</v>
+        <v>4.632053731634787</v>
       </c>
       <c r="K5" t="n">
-        <v>13.99136050052902</v>
+        <v>12.87888232929496</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48041698201394</v>
+        <v>44.3753677816055</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84727176611943</v>
+        <v>99.80878700805199</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.81549280614168</v>
+        <v>85.52694586917708</v>
       </c>
       <c r="C6" t="n">
-        <v>41.89522860843182</v>
+        <v>41.85244230606413</v>
       </c>
       <c r="D6" t="n">
-        <v>2.07393540846742</v>
+        <v>2.042172989593628</v>
       </c>
       <c r="E6" t="n">
-        <v>7.538227220146767</v>
+        <v>7.845886711119532</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469173820929136</v>
+        <v>0.7425150101814867</v>
       </c>
       <c r="G6" t="n">
-        <v>31.59922293324004</v>
+        <v>31.30016004717299</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35819957627402</v>
+        <v>34.15569046834839</v>
       </c>
       <c r="I6" t="n">
-        <v>3.830756647839805</v>
+        <v>4.799801829126761</v>
       </c>
       <c r="J6" t="n">
-        <v>4.66823363808071</v>
+        <v>4.640718813634293</v>
       </c>
       <c r="K6" t="n">
-        <v>15.18450719385833</v>
+        <v>14.47305413082292</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79276426385174</v>
+        <v>43.51480890612437</v>
       </c>
       <c r="M6" t="n">
-        <v>99.8725000661419</v>
+        <v>99.84030534301142</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.42787437104488</v>
+        <v>83.82255793477481</v>
       </c>
       <c r="C7" t="n">
-        <v>41.10273404327255</v>
+        <v>40.89298596659964</v>
       </c>
       <c r="D7" t="n">
-        <v>2.006663882354901</v>
+        <v>1.960785727352514</v>
       </c>
       <c r="E7" t="n">
-        <v>7.826441364240216</v>
+        <v>8.200903691156611</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478712708608319</v>
+        <v>0.743697933167814</v>
       </c>
       <c r="G7" t="n">
-        <v>30.57424985933915</v>
+        <v>30.05274646030784</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40207845959826</v>
+        <v>34.21010492571944</v>
       </c>
       <c r="I7" t="n">
-        <v>3.196374091771317</v>
+        <v>4.006207114771746</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674195442880199</v>
+        <v>4.648112082298838</v>
       </c>
       <c r="K7" t="n">
-        <v>16.57212562895512</v>
+        <v>16.17744206522519</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21873042088789</v>
+        <v>42.79624413958832</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89359009311556</v>
+        <v>99.86667217141314</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.40274441231358</v>
+        <v>81.99502459682068</v>
       </c>
       <c r="C8" t="n">
-        <v>43.43702215043626</v>
+        <v>39.68701812886005</v>
       </c>
       <c r="D8" t="n">
-        <v>2.010985597487832</v>
+        <v>1.874222082020495</v>
       </c>
       <c r="E8" t="n">
-        <v>9.685089327929141</v>
+        <v>8.396028742116798</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494819474754779</v>
+        <v>0.7447086506911913</v>
       </c>
       <c r="G8" t="n">
-        <v>31.08501479403617</v>
+        <v>28.72599502104898</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47616958387197</v>
+        <v>34.2565979317948</v>
       </c>
       <c r="I8" t="n">
-        <v>5.711740989791259</v>
+        <v>3.343043102328467</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684262171721737</v>
+        <v>4.654429066819946</v>
       </c>
       <c r="K8" t="n">
-        <v>11.5972555876864</v>
+        <v>18.00497540317932</v>
       </c>
       <c r="L8" t="n">
-        <v>44.77574005673544</v>
+        <v>42.19672293699473</v>
       </c>
       <c r="M8" t="n">
-        <v>99.8100177948581</v>
+        <v>99.88871646903411</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.65470759477857</v>
+        <v>79.97073767896538</v>
       </c>
       <c r="C9" t="n">
-        <v>42.57583220908683</v>
+        <v>38.18097912001222</v>
       </c>
       <c r="D9" t="n">
-        <v>1.932354679142095</v>
+        <v>1.778997386205941</v>
       </c>
       <c r="E9" t="n">
-        <v>10.10114818479347</v>
+        <v>8.434298135796109</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508567202263109</v>
+        <v>0.7455744143844084</v>
       </c>
       <c r="G9" t="n">
-        <v>29.86956936116022</v>
+        <v>27.26649661683593</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53940913041028</v>
+        <v>34.29642306168279</v>
       </c>
       <c r="I9" t="n">
-        <v>4.768515017631748</v>
+        <v>2.78910797415765</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692854501414443</v>
+        <v>4.659840089902553</v>
       </c>
       <c r="K9" t="n">
-        <v>13.34529240522143</v>
+        <v>20.02926232103463</v>
       </c>
       <c r="L9" t="n">
-        <v>43.92021591375309</v>
+        <v>41.69689625055513</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84134052806134</v>
+        <v>99.90713769160199</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.71658635139288</v>
+        <v>85.37690721515195</v>
       </c>
       <c r="C10" t="n">
-        <v>41.37810145438527</v>
+        <v>41.84108551960688</v>
       </c>
       <c r="D10" t="n">
-        <v>1.845864576663766</v>
+        <v>1.781026148160135</v>
       </c>
       <c r="E10" t="n">
-        <v>10.31236263725277</v>
+        <v>10.49724649997101</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520325619093663</v>
+        <v>0.7464246646532687</v>
       </c>
       <c r="G10" t="n">
-        <v>28.53263978869827</v>
+        <v>28.86410362399089</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59349784783083</v>
+        <v>35.90204697061775</v>
       </c>
       <c r="I10" t="n">
-        <v>3.979985427104337</v>
+        <v>2.92090515367597</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700203511933539</v>
+        <v>4.66515415408293</v>
       </c>
       <c r="K10" t="n">
-        <v>15.28341364860711</v>
+        <v>14.62309278484807</v>
       </c>
       <c r="L10" t="n">
-        <v>43.20602614651785</v>
+        <v>43.43856909692165</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86754124951023</v>
+        <v>99.90274740137659</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.54403799372859</v>
+        <v>84.99983755690484</v>
       </c>
       <c r="C11" t="n">
-        <v>39.82312696062438</v>
+        <v>41.78679729009903</v>
       </c>
       <c r="D11" t="n">
-        <v>1.749654405723491</v>
+        <v>1.753294418399411</v>
       </c>
       <c r="E11" t="n">
-        <v>10.32837867975816</v>
+        <v>10.83002689018459</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530411456836482</v>
+        <v>0.7471515642579067</v>
       </c>
       <c r="G11" t="n">
-        <v>27.04546126750387</v>
+        <v>28.49701815082148</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63989270144781</v>
+        <v>36.01935718817528</v>
       </c>
       <c r="I11" t="n">
-        <v>3.321102633088821</v>
+        <v>2.483292068454262</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706507160522801</v>
+        <v>4.669697276611918</v>
       </c>
       <c r="K11" t="n">
-        <v>17.4559620062714</v>
+        <v>15.00016244309518</v>
       </c>
       <c r="L11" t="n">
-        <v>42.61035588235131</v>
+        <v>43.13034439722575</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8894448492471</v>
+        <v>99.91730413041995</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.17108223273243</v>
+        <v>82.9555737647828</v>
       </c>
       <c r="C12" t="n">
-        <v>37.96484399226868</v>
+        <v>40.12812890771558</v>
       </c>
       <c r="D12" t="n">
-        <v>1.645426077525483</v>
+        <v>1.66743248570595</v>
       </c>
       <c r="E12" t="n">
-        <v>10.17490445021787</v>
+        <v>10.64485000590326</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539086682621501</v>
+        <v>0.7477733628291984</v>
       </c>
       <c r="G12" t="n">
-        <v>25.43434126344212</v>
+        <v>27.10146870473138</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67979874005889</v>
+        <v>36.04933341510147</v>
       </c>
       <c r="I12" t="n">
-        <v>2.770773856587469</v>
+        <v>2.07113227282906</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711929176638438</v>
+        <v>4.67358351768249</v>
       </c>
       <c r="K12" t="n">
-        <v>19.82891776726756</v>
+        <v>17.04442623521719</v>
       </c>
       <c r="L12" t="n">
-        <v>42.11398538954463</v>
+        <v>42.75846452183242</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90774714908088</v>
+        <v>99.93101966476519</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.93400771317367</v>
+        <v>84.26256466596953</v>
       </c>
       <c r="C13" t="n">
-        <v>36.15633564219268</v>
+        <v>41.19557405556187</v>
       </c>
       <c r="D13" t="n">
-        <v>1.548150187599273</v>
+        <v>1.668702034625453</v>
       </c>
       <c r="E13" t="n">
-        <v>9.958584737612991</v>
+        <v>11.33076265106859</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546539481797164</v>
+        <v>0.7483427021415548</v>
       </c>
       <c r="G13" t="n">
-        <v>23.9306892824251</v>
+        <v>27.47913213348208</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71408161626695</v>
+        <v>36.43380956465034</v>
       </c>
       <c r="I13" t="n">
-        <v>2.311260764966423</v>
+        <v>1.924673691616816</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716587176123228</v>
+        <v>4.677141888384718</v>
       </c>
       <c r="K13" t="n">
-        <v>22.06599228682633</v>
+        <v>15.73743533403046</v>
       </c>
       <c r="L13" t="n">
-        <v>41.70070613052022</v>
+        <v>43.00288363042775</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92303405953923</v>
+        <v>99.93589302002006</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.23900272106761</v>
+        <v>82.17616426238126</v>
       </c>
       <c r="C14" t="n">
-        <v>39.93087228734333</v>
+        <v>39.40785490823173</v>
       </c>
       <c r="D14" t="n">
-        <v>1.550092354966942</v>
+        <v>1.583721984257956</v>
       </c>
       <c r="E14" t="n">
-        <v>12.10701644043436</v>
+        <v>11.02122387914305</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556006678738243</v>
+        <v>0.748829884901741</v>
       </c>
       <c r="G14" t="n">
-        <v>25.56825643755624</v>
+        <v>26.07973428754935</v>
       </c>
       <c r="H14" t="n">
-        <v>36.36517662733306</v>
+        <v>36.4575285424088</v>
       </c>
       <c r="I14" t="n">
-        <v>3.170356018691796</v>
+        <v>1.604938903484495</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722504174211402</v>
+        <v>4.680186780635881</v>
       </c>
       <c r="K14" t="n">
-        <v>15.76099727893238</v>
+        <v>17.82383573761874</v>
       </c>
       <c r="L14" t="n">
-        <v>44.20258430826566</v>
+        <v>42.71484619604907</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89445387454137</v>
+        <v>99.94653684189953</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.55587321602154</v>
+        <v>81.29596854066176</v>
       </c>
       <c r="C15" t="n">
-        <v>39.73816362060361</v>
+        <v>38.74126818628547</v>
       </c>
       <c r="D15" t="n">
-        <v>1.524703708447043</v>
+        <v>1.545787622238137</v>
       </c>
       <c r="E15" t="n">
-        <v>12.34950989402651</v>
+        <v>10.99815197451888</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563978891116656</v>
+        <v>0.7492468166320664</v>
       </c>
       <c r="G15" t="n">
-        <v>25.14947918035399</v>
+        <v>25.46965204447018</v>
       </c>
       <c r="H15" t="n">
-        <v>36.40354489824359</v>
+        <v>36.49242417241727</v>
       </c>
       <c r="I15" t="n">
-        <v>2.644750838890848</v>
+        <v>1.357913306434799</v>
       </c>
       <c r="J15" t="n">
-        <v>4.72748680694791</v>
+        <v>4.682792603950415</v>
       </c>
       <c r="K15" t="n">
-        <v>16.44412678397844</v>
+        <v>18.70403145933826</v>
       </c>
       <c r="L15" t="n">
-        <v>43.72964415045429</v>
+        <v>42.50946176532962</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91193455503634</v>
+        <v>99.95476141095334</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.25752330056343</v>
+        <v>78.78201701187398</v>
       </c>
       <c r="C16" t="n">
-        <v>37.8490672618826</v>
+        <v>36.43748599940967</v>
       </c>
       <c r="D16" t="n">
-        <v>1.436202825968505</v>
+        <v>1.444251592429699</v>
       </c>
       <c r="E16" t="n">
-        <v>12.00034590818426</v>
+        <v>10.46442087412457</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570823707701267</v>
+        <v>0.7496057181858274</v>
       </c>
       <c r="G16" t="n">
-        <v>23.68968663901888</v>
+        <v>23.79666197002938</v>
       </c>
       <c r="H16" t="n">
-        <v>36.43648729422922</v>
+        <v>36.50990464406593</v>
       </c>
       <c r="I16" t="n">
-        <v>2.205953445079144</v>
+        <v>1.132136474377142</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731764817313293</v>
+        <v>4.685035738661422</v>
       </c>
       <c r="K16" t="n">
-        <v>18.74247669943656</v>
+        <v>21.21798298812602</v>
       </c>
       <c r="L16" t="n">
-        <v>43.33499073760053</v>
+        <v>42.30681119839669</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92653469891968</v>
+        <v>99.96228018593239</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.73579972371012</v>
+        <v>83.97115249491796</v>
       </c>
       <c r="C17" t="n">
-        <v>38.93428053321664</v>
+        <v>39.84058502610412</v>
       </c>
       <c r="D17" t="n">
-        <v>1.437487793893446</v>
+        <v>1.445001998508602</v>
       </c>
       <c r="E17" t="n">
-        <v>12.722093041507</v>
+        <v>12.2726345812071</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577597309210662</v>
+        <v>0.7499951992780797</v>
       </c>
       <c r="G17" t="n">
-        <v>24.05177439331544</v>
+        <v>25.39365366893942</v>
       </c>
       <c r="H17" t="n">
-        <v>36.80997958672289</v>
+        <v>38.11350190577068</v>
       </c>
       <c r="I17" t="n">
-        <v>2.22070685909363</v>
+        <v>1.308895145726078</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735998318256664</v>
+        <v>4.687469995487998</v>
       </c>
       <c r="K17" t="n">
-        <v>17.26420027628988</v>
+        <v>16.02884750508204</v>
       </c>
       <c r="L17" t="n">
-        <v>43.72756179806142</v>
+        <v>44.08696028809737</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92604260756794</v>
+        <v>99.95639281928354</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.56972067644519</v>
+        <v>85.70925826547058</v>
       </c>
       <c r="C18" t="n">
-        <v>37.11146742057944</v>
+        <v>40.59442042876933</v>
       </c>
       <c r="D18" t="n">
-        <v>1.357040211780844</v>
+        <v>1.446261491005153</v>
       </c>
       <c r="E18" t="n">
-        <v>12.31878152430978</v>
+        <v>12.89702414275168</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7583403362692945</v>
+        <v>0.7506489100182135</v>
       </c>
       <c r="G18" t="n">
-        <v>22.70574063659094</v>
+        <v>25.53586878964399</v>
       </c>
       <c r="H18" t="n">
-        <v>36.83818387120004</v>
+        <v>38.14672239246699</v>
       </c>
       <c r="I18" t="n">
-        <v>1.852006994611171</v>
+        <v>2.241176851970738</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739627101683092</v>
+        <v>4.691555687613834</v>
       </c>
       <c r="K18" t="n">
-        <v>19.43027932355484</v>
+        <v>14.2907417345294</v>
       </c>
       <c r="L18" t="n">
-        <v>43.39656695422424</v>
+        <v>45.04019700007409</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93831369835851</v>
+        <v>99.9253591633728</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.72087215892222</v>
+        <v>82.9423692581607</v>
       </c>
       <c r="C19" t="n">
-        <v>36.54827738512394</v>
+        <v>38.17418888888283</v>
       </c>
       <c r="D19" t="n">
-        <v>1.326233808251339</v>
+        <v>1.346928189249907</v>
       </c>
       <c r="E19" t="n">
-        <v>12.29652003309442</v>
+        <v>12.32272867168545</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7588300165124574</v>
+        <v>0.7512127555512642</v>
       </c>
       <c r="G19" t="n">
-        <v>22.19029370847878</v>
+        <v>23.78199359083665</v>
       </c>
       <c r="H19" t="n">
-        <v>36.86197125263418</v>
+        <v>38.17537607960949</v>
       </c>
       <c r="I19" t="n">
-        <v>1.544335736748199</v>
+        <v>1.869050249032528</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742687603202859</v>
+        <v>4.695079722195401</v>
       </c>
       <c r="K19" t="n">
-        <v>20.27912784107775</v>
+        <v>17.05763074183931</v>
       </c>
       <c r="L19" t="n">
-        <v>43.12115013505911</v>
+        <v>44.70592545672311</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9485553612608</v>
+        <v>99.93774508744525</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.38843596317268</v>
+        <v>79.9684787474103</v>
       </c>
       <c r="C20" t="n">
-        <v>34.45393244513579</v>
+        <v>35.48856300893855</v>
       </c>
       <c r="D20" t="n">
-        <v>1.240546367149019</v>
+        <v>1.240779391619358</v>
       </c>
       <c r="E20" t="n">
-        <v>11.7166567816339</v>
+        <v>11.61135728654938</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7592508869863845</v>
+        <v>0.7517007834448453</v>
       </c>
       <c r="G20" t="n">
-        <v>20.75658762033772</v>
+        <v>21.90778081166052</v>
       </c>
       <c r="H20" t="n">
-        <v>36.88241603601569</v>
+        <v>38.20017684109433</v>
       </c>
       <c r="I20" t="n">
-        <v>1.287660227385054</v>
+        <v>1.558553736511619</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745318043664904</v>
+        <v>4.698129896530283</v>
       </c>
       <c r="K20" t="n">
-        <v>22.61156403682732</v>
+        <v>20.03152125258966</v>
       </c>
       <c r="L20" t="n">
-        <v>42.8916053031272</v>
+        <v>44.42799767599866</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95710178509032</v>
+        <v>99.94808193752687</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.74614734451288</v>
+        <v>77.04666995237029</v>
       </c>
       <c r="C21" t="n">
-        <v>37.65385103132368</v>
+        <v>32.80627527497176</v>
       </c>
       <c r="D21" t="n">
-        <v>1.241533036718635</v>
+        <v>1.137122356246875</v>
       </c>
       <c r="E21" t="n">
-        <v>13.48217579171718</v>
+        <v>10.85791024028341</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7598547578014793</v>
+        <v>0.7521234077913963</v>
       </c>
       <c r="G21" t="n">
-        <v>22.20023546635771</v>
+        <v>20.07756375142782</v>
       </c>
       <c r="H21" t="n">
-        <v>38.33888957287959</v>
+        <v>38.22165390368513</v>
       </c>
       <c r="I21" t="n">
-        <v>1.974366482779052</v>
+        <v>1.299524994239439</v>
       </c>
       <c r="J21" t="n">
-        <v>4.749092236259246</v>
+        <v>4.700771298696226</v>
       </c>
       <c r="K21" t="n">
-        <v>17.25385265548712</v>
+        <v>22.95333004762973</v>
       </c>
       <c r="L21" t="n">
-        <v>45.02653639929796</v>
+        <v>44.19710151805096</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93424008610876</v>
+        <v>99.95670684065243</v>
       </c>
     </row>
   </sheetData>
